--- a/reports/빅딜/history/2026-04-17/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/history/2026-04-17/빅딜_training_mgf_report.xlsx
@@ -84,108 +84,108 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>381</t>
+  </si>
+  <si>
+    <t>12위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>171조 6820억 7377만</t>
+  </si>
+  <si>
+    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
+  </si>
+  <si>
+    <t>망겜감별사</t>
+  </si>
+  <si>
+    <t>2026.04.17</t>
+  </si>
+  <si>
+    <t>초코나라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B4%88%EC%BD%94%EB%82%98%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>Scania 18</t>
+  </si>
+  <si>
+    <t>387</t>
+  </si>
+  <si>
+    <t>8위</t>
+  </si>
+  <si>
+    <t>167조 6081억 6238만</t>
+  </si>
+  <si>
+    <t>초코남</t>
+  </si>
+  <si>
+    <t>블랙소울</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%9E%99%EC%86%8C%EC%9A%B8</t>
+  </si>
+  <si>
+    <t>Scania 31</t>
+  </si>
+  <si>
     <t>380</t>
   </si>
   <si>
-    <t>12위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>171조 6820억 7377만</t>
-  </si>
-  <si>
-    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
-  </si>
-  <si>
-    <t>망겜감별사</t>
-  </si>
-  <si>
-    <t>2026.04.17</t>
-  </si>
-  <si>
-    <t>초코나라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B4%88%EC%BD%94%EB%82%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>Scania 18</t>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>171조 9975억 7642만</t>
+  </si>
+  <si>
+    <t>보심</t>
+  </si>
+  <si>
+    <t>다다익선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%84%A0</t>
+  </si>
+  <si>
+    <t>Scania 25</t>
   </si>
   <si>
     <t>386</t>
   </si>
   <si>
-    <t>8위</t>
-  </si>
-  <si>
-    <t>167조 6081억 6238만</t>
-  </si>
-  <si>
-    <t>초코남</t>
-  </si>
-  <si>
-    <t>블랙소울</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%9E%99%EC%86%8C%EC%9A%B8</t>
-  </si>
-  <si>
-    <t>Scania 31</t>
-  </si>
-  <si>
-    <t>379</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>171조 9975억 7642만</t>
-  </si>
-  <si>
-    <t>보심</t>
-  </si>
-  <si>
-    <t>다다익선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%84%A0</t>
-  </si>
-  <si>
-    <t>Scania 25</t>
+    <t>7위</t>
+  </si>
+  <si>
+    <t>169조 3419억 6601만</t>
+  </si>
+  <si>
+    <t>2일 미접 여부 확인 길드컨텐츠 갱신 여부 확인,전투력 5000억 이상 재밌게 소통하면서 게임하실 분 귓주세요</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>비련</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%84%EB%A0%A8</t>
+  </si>
+  <si>
+    <t>Scania 27</t>
   </si>
   <si>
     <t>385</t>
   </si>
   <si>
-    <t>7위</t>
-  </si>
-  <si>
-    <t>169조 3419억 6601만</t>
-  </si>
-  <si>
-    <t>2일 미접 여부 확인 길드컨텐츠 갱신 여부 확인,전투력 5000억 이상 재밌게 소통하면서 게임하실 분 귓주세요</t>
-  </si>
-  <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
-    <t>비련</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%84%EB%A0%A8</t>
-  </si>
-  <si>
-    <t>Scania 27</t>
-  </si>
-  <si>
-    <t>384</t>
-  </si>
-  <si>
     <t>34위</t>
   </si>
   <si>
@@ -204,7 +204,7 @@
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%80%ED%81%AC%EB%9F%B0</t>
   </si>
   <si>
-    <t>381</t>
+    <t>382</t>
   </si>
   <si>
     <t>33위</t>
@@ -231,7 +231,7 @@
     <t>Scania 33</t>
   </si>
   <si>
-    <t>382</t>
+    <t>383</t>
   </si>
   <si>
     <t>Lv.6</t>
@@ -285,7 +285,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>22조 5686억 1996만</t>
+    <t>22조 7699억 4133만</t>
   </si>
   <si>
     <t>2</t>
@@ -435,12 +435,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>4조 5125억 6849만</t>
+    <t>4조 9239억 3208만</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
+    <t>4조 3189억 8200만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>뻥뻥</t>
   </si>
   <si>
@@ -453,7 +465,7 @@
     <t>4조 2010억 1283만</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>므고</t>
@@ -465,7 +477,7 @@
     <t>4조 1502억 5010만</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>아르젠타</t>
@@ -480,7 +492,7 @@
     <t>3조 6989억 1308만</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -495,18 +507,6 @@
     <t>3조 6112억 850만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
-    <t>3조 5215억 9190만</t>
-  </si>
-  <si>
     <t>17</t>
   </si>
   <si>
@@ -546,6 +546,18 @@
     <t>20</t>
   </si>
   <si>
+    <t>덕르코프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>2조 7646억 9816만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>겨울바다</t>
   </si>
   <si>
@@ -555,21 +567,21 @@
     <t>2조 7544억 9536만</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>덕르코프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
-  </si>
-  <si>
-    <t>2조 7199억 9178만</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
+    <t>여븨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
+  </si>
+  <si>
+    <t>2조 5691억 3500만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>강철고튠데</t>
   </si>
   <si>
@@ -577,18 +589,6 @@
   </si>
   <si>
     <t>2조 5595억 2만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>여븨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
-  </si>
-  <si>
-    <t>2조 3162억 528만</t>
   </si>
   <si>
     <t>24</t>
@@ -3447,13 +3447,13 @@
         <v>88</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3464,25 +3464,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>143</v>
@@ -3511,13 +3511,13 @@
         <v>88</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3528,16 +3528,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>88</v>
@@ -3546,10 +3546,10 @@
         <v>119</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3560,16 +3560,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>88</v>
@@ -3578,7 +3578,7 @@
         <v>119</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>157</v>
@@ -3642,7 +3642,7 @@
         <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>165</v>
@@ -3703,10 +3703,10 @@
         <v>88</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>173</v>
@@ -3735,10 +3735,10 @@
         <v>88</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>177</v>
@@ -3767,10 +3767,10 @@
         <v>88</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>181</v>
@@ -3799,10 +3799,10 @@
         <v>88</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>185</v>
@@ -3834,7 +3834,7 @@
         <v>82</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>189</v>
@@ -3866,7 +3866,7 @@
         <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>193</v>
@@ -3898,7 +3898,7 @@
         <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>197</v>
@@ -3930,7 +3930,7 @@
         <v>201</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>202</v>
@@ -3962,7 +3962,7 @@
         <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>206</v>
@@ -4207,7 +4207,7 @@
         <v>119</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>224</v>
@@ -4509,7 +4509,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>252</v>
@@ -4559,7 +4559,7 @@
         <v>82</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>257</v>
@@ -4573,7 +4573,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>258</v>
@@ -4605,7 +4605,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>261</v>
@@ -4687,7 +4687,7 @@
         <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>269</v>
@@ -4783,7 +4783,7 @@
         <v>119</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>278</v>
@@ -4847,7 +4847,7 @@
         <v>119</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>284</v>
@@ -4879,7 +4879,7 @@
         <v>82</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>287</v>
@@ -4943,7 +4943,7 @@
         <v>129</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>293</v>
@@ -4975,7 +4975,7 @@
         <v>119</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>296</v>
@@ -5007,7 +5007,7 @@
         <v>119</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>299</v>
@@ -5347,7 +5347,7 @@
         <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>323</v>
@@ -5475,7 +5475,7 @@
         <v>82</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>334</v>
@@ -5507,7 +5507,7 @@
         <v>82</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>337</v>
@@ -5521,7 +5521,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>338</v>
@@ -5539,7 +5539,7 @@
         <v>82</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>340</v>
@@ -5571,7 +5571,7 @@
         <v>100</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>343</v>
@@ -5585,7 +5585,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>344</v>
@@ -5617,7 +5617,7 @@
         <v>32</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>347</v>
@@ -5635,7 +5635,7 @@
         <v>119</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>349</v>
@@ -5667,7 +5667,7 @@
         <v>217</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>352</v>
@@ -5699,7 +5699,7 @@
         <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>355</v>
@@ -5763,7 +5763,7 @@
         <v>82</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>361</v>
@@ -5827,7 +5827,7 @@
         <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>367</v>
@@ -5923,7 +5923,7 @@
         <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>376</v>
@@ -6296,7 +6296,7 @@
         <v>119</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>406</v>
@@ -6328,7 +6328,7 @@
         <v>82</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>408</v>
@@ -6392,7 +6392,7 @@
         <v>82</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>414</v>
@@ -6424,7 +6424,7 @@
         <v>82</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>417</v>
@@ -6456,7 +6456,7 @@
         <v>119</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>420</v>
@@ -6488,7 +6488,7 @@
         <v>82</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>423</v>
@@ -6520,7 +6520,7 @@
         <v>82</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>426</v>
@@ -6552,7 +6552,7 @@
         <v>201</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>429</v>
@@ -6566,7 +6566,7 @@
         <v>39</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>430</v>
@@ -6584,7 +6584,7 @@
         <v>129</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>432</v>
@@ -6616,7 +6616,7 @@
         <v>119</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>435</v>
@@ -6630,7 +6630,7 @@
         <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>436</v>
@@ -6648,7 +6648,7 @@
         <v>201</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>438</v>
@@ -6662,7 +6662,7 @@
         <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>439</v>
@@ -6680,7 +6680,7 @@
         <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>441</v>
@@ -6712,7 +6712,7 @@
         <v>106</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>444</v>
@@ -6744,7 +6744,7 @@
         <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>447</v>
@@ -6776,7 +6776,7 @@
         <v>119</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>450</v>
@@ -6808,7 +6808,7 @@
         <v>119</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>453</v>
@@ -6840,7 +6840,7 @@
         <v>82</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>456</v>
@@ -6904,7 +6904,7 @@
         <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>462</v>
@@ -6968,7 +6968,7 @@
         <v>201</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>468</v>
@@ -7000,7 +7000,7 @@
         <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>471</v>
@@ -7032,7 +7032,7 @@
         <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>474</v>
@@ -7064,7 +7064,7 @@
         <v>82</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>477</v>
@@ -7096,7 +7096,7 @@
         <v>129</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>480</v>
@@ -7406,7 +7406,7 @@
         <v>393</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>502</v>
@@ -7534,7 +7534,7 @@
         <v>82</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>514</v>
@@ -7566,7 +7566,7 @@
         <v>119</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>517</v>
@@ -7630,7 +7630,7 @@
         <v>82</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>523</v>
@@ -7644,7 +7644,7 @@
         <v>47</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>524</v>
@@ -7662,7 +7662,7 @@
         <v>217</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>526</v>
@@ -7694,7 +7694,7 @@
         <v>119</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>529</v>
@@ -7708,7 +7708,7 @@
         <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>530</v>
@@ -7726,7 +7726,7 @@
         <v>89</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>532</v>
@@ -7740,7 +7740,7 @@
         <v>47</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>533</v>
@@ -7758,7 +7758,7 @@
         <v>119</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>535</v>
@@ -7790,7 +7790,7 @@
         <v>82</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>538</v>
@@ -7822,7 +7822,7 @@
         <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>541</v>
@@ -7854,7 +7854,7 @@
         <v>119</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>544</v>
@@ -7886,7 +7886,7 @@
         <v>217</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>547</v>
@@ -7918,7 +7918,7 @@
         <v>217</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>550</v>
@@ -8078,7 +8078,7 @@
         <v>100</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>565</v>
@@ -8451,7 +8451,7 @@
         <v>82</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>591</v>
@@ -8483,7 +8483,7 @@
         <v>217</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>594</v>
@@ -8515,7 +8515,7 @@
         <v>393</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>597</v>
@@ -8547,7 +8547,7 @@
         <v>119</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>600</v>
@@ -8579,7 +8579,7 @@
         <v>119</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>603</v>
@@ -8643,7 +8643,7 @@
         <v>217</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>609</v>
@@ -8689,7 +8689,7 @@
         <v>55</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>613</v>
@@ -8753,7 +8753,7 @@
         <v>55</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>619</v>
@@ -8785,7 +8785,7 @@
         <v>55</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>623</v>
@@ -9367,7 +9367,7 @@
         <v>393</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>674</v>
@@ -9431,7 +9431,7 @@
         <v>119</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>679</v>
@@ -9495,7 +9495,7 @@
         <v>82</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>685</v>
@@ -9591,7 +9591,7 @@
         <v>106</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>694</v>
@@ -9701,7 +9701,7 @@
         <v>63</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>704</v>
@@ -9765,7 +9765,7 @@
         <v>63</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>710</v>
@@ -9797,7 +9797,7 @@
         <v>63</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>713</v>
